--- a/任务列表.xlsx
+++ b/任务列表.xlsx
@@ -2,14 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <fileSharing readOnlyRecommended="1"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Minecraft\PCL2\.minecraft\versions\1.21.4-Fabric 0.16.9\saves\YWSJ\datapacks\sctz_ywsj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790978A9-F1FC-4B72-8798-9D97DE7DECED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E204CB-6B92-4A7D-8465-240B698A0605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3067,7 +3066,7 @@
         <v>223</v>
       </c>
       <c r="L1" s="2" t="str">
-        <f>A1&amp;B1&amp;C1&amp;D1&amp;E1&amp;F1&amp;G1&amp;H1&amp;I1&amp;J1&amp;K1</f>
+        <f t="shared" ref="L1:L64" si="0">A1&amp;B1&amp;C1&amp;D1&amp;E1&amp;F1&amp;G1&amp;H1&amp;I1&amp;J1&amp;K1</f>
         <v>data modify storage ywsj:eventlist args.e0 set value {id:0,text:"放置一个石头",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3106,7 +3105,7 @@
         <v>223</v>
       </c>
       <c r="L2" s="2" t="str">
-        <f>A2&amp;B2&amp;C2&amp;D2&amp;E2&amp;F2&amp;G2&amp;H2&amp;I2&amp;J2&amp;K2</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e1 set value {id:1,text:"物品栏仅包含1组堆叠圆石其余位置留空(拾取刷新判定)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3145,7 +3144,7 @@
         <v>223</v>
       </c>
       <c r="L3" s="2" t="str">
-        <f>A3&amp;B3&amp;C3&amp;D3&amp;E3&amp;F3&amp;G3&amp;H3&amp;I3&amp;J3&amp;K3</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e2 set value {id:2,text:"击败一只僵尸",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3184,7 +3183,7 @@
         <v>223</v>
       </c>
       <c r="L4" s="2" t="str">
-        <f>A4&amp;B4&amp;C4&amp;D4&amp;E4&amp;F4&amp;G4&amp;H4&amp;I4&amp;J4&amp;K4</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e3 set value {id:3,text:"被苦力怕炸死",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3223,7 +3222,7 @@
         <v>223</v>
       </c>
       <c r="L5" s="2" t="str">
-        <f>A5&amp;B5&amp;C5&amp;D5&amp;E5&amp;F5&amp;G5&amp;H5&amp;I5&amp;J5&amp;K5</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e4 set value {id:4,text:"食用一个苹果",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3262,7 +3261,7 @@
         <v>223</v>
       </c>
       <c r="L6" s="2" t="str">
-        <f>A6&amp;B6&amp;C6&amp;D6&amp;E6&amp;F6&amp;G6&amp;H6&amp;I6&amp;J6&amp;K6</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e5 set value {id:5,text:"繁殖一只绵羊",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3301,7 +3300,7 @@
         <v>223</v>
       </c>
       <c r="L7" s="2" t="str">
-        <f>A7&amp;B7&amp;C7&amp;D7&amp;E7&amp;F7&amp;G7&amp;H7&amp;I7&amp;J7&amp;K7</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e6 set value {id:6,text:"物品栏包含一组堆叠的任意木板(拾取刷新判定)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3340,7 +3339,7 @@
         <v>223</v>
       </c>
       <c r="L8" s="2" t="str">
-        <f>A8&amp;B8&amp;C8&amp;D8&amp;E8&amp;F8&amp;G8&amp;H8&amp;I8&amp;J8&amp;K8</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e7 set value {id:7,text:"召唤一只铁傀儡",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3379,7 +3378,7 @@
         <v>223</v>
       </c>
       <c r="L9" s="2" t="str">
-        <f>A9&amp;B9&amp;C9&amp;D9&amp;E9&amp;F9&amp;G9&amp;H9&amp;I9&amp;J9&amp;K9</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e8 set value {id:8,text:"召唤一只雪傀儡",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3418,7 +3417,7 @@
         <v>223</v>
       </c>
       <c r="L10" s="2" t="str">
-        <f>A10&amp;B10&amp;C10&amp;D10&amp;E10&amp;F10&amp;G10&amp;H10&amp;I10&amp;J10&amp;K10</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e9 set value {id:9,text:"驯服一只马",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3457,7 +3456,7 @@
         <v>223</v>
       </c>
       <c r="L11" s="2" t="str">
-        <f>A11&amp;B11&amp;C11&amp;D11&amp;E11&amp;F11&amp;G11&amp;H11&amp;I11&amp;J11&amp;K11</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e10 set value {id:10,text:"拾取一个铁锭(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3496,7 +3495,7 @@
         <v>223</v>
       </c>
       <c r="L12" s="2" t="str">
-        <f>A12&amp;B12&amp;C12&amp;D12&amp;E12&amp;F12&amp;G12&amp;H12&amp;I12&amp;J12&amp;K12</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e11 set value {id:11,text:"对自己造成燃烧伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3535,7 +3534,7 @@
         <v>223</v>
       </c>
       <c r="L13" s="2" t="str">
-        <f>A13&amp;B13&amp;C13&amp;D13&amp;E13&amp;F13&amp;G13&amp;H13&amp;I13&amp;J13&amp;K13</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e12 set value {id:12,text:"物品栏包含大于32个堆叠任意主世界原木(拾取刷新判定)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3574,7 +3573,7 @@
         <v>223</v>
       </c>
       <c r="L14" s="2" t="str">
-        <f>A14&amp;B14&amp;C14&amp;D14&amp;E14&amp;F14&amp;G14&amp;H14&amp;I14&amp;J14&amp;K14</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e13 set value {id:13,text:"放置一个泥土",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3613,7 +3612,7 @@
         <v>223</v>
       </c>
       <c r="L15" s="2" t="str">
-        <f>A15&amp;B15&amp;C15&amp;D15&amp;E15&amp;F15&amp;G15&amp;H15&amp;I15&amp;J15&amp;K15</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e14 set value {id:14,text:"放置一个玻璃",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3652,7 +3651,7 @@
         <v>223</v>
       </c>
       <c r="L16" s="2" t="str">
-        <f>A16&amp;B16&amp;C16&amp;D16&amp;E16&amp;F16&amp;G16&amp;H16&amp;I16&amp;J16&amp;K16</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e15 set value {id:15,text:"放置一个沙子",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3691,7 +3690,7 @@
         <v>223</v>
       </c>
       <c r="L17" s="2" t="str">
-        <f>A17&amp;B17&amp;C17&amp;D17&amp;E17&amp;F17&amp;G17&amp;H17&amp;I17&amp;J17&amp;K17</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e16 set value {id:16,text:"一次性掉落超过10格",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3730,7 +3729,7 @@
         <v>223</v>
       </c>
       <c r="L18" s="2" t="str">
-        <f>A18&amp;B18&amp;C18&amp;D18&amp;E18&amp;F18&amp;G18&amp;H18&amp;I18&amp;J18&amp;K18</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e17 set value {id:17,text:"放置一个铁块",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3769,7 +3768,7 @@
         <v>223</v>
       </c>
       <c r="L19" s="2" t="str">
-        <f>A19&amp;B19&amp;C19&amp;D19&amp;E19&amp;F19&amp;G19&amp;H19&amp;I19&amp;J19&amp;K19</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e18 set value {id:18,text:"拾取一个金锭(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3808,7 +3807,7 @@
         <v>223</v>
       </c>
       <c r="L20" s="2" t="str">
-        <f>A20&amp;B20&amp;C20&amp;D20&amp;E20&amp;F20&amp;G20&amp;H20&amp;I20&amp;J20&amp;K20</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e19 set value {id:19,text:"拾取一个铜锭(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3847,7 +3846,7 @@
         <v>223</v>
       </c>
       <c r="L21" s="2" t="str">
-        <f>A21&amp;B21&amp;C21&amp;D21&amp;E21&amp;F21&amp;G21&amp;H21&amp;I21&amp;J21&amp;K21</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e20 set value {id:20,text:"使用木质锄头锄地",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3886,7 +3885,7 @@
         <v>223</v>
       </c>
       <c r="L22" s="2" t="str">
-        <f>A22&amp;B22&amp;C22&amp;D22&amp;E22&amp;F22&amp;G22&amp;H22&amp;I22&amp;J22&amp;K22</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e21 set value {id:21,text:"使用钻石锄头锄地",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3925,7 +3924,7 @@
         <v>223</v>
       </c>
       <c r="L23" s="2" t="str">
-        <f>A23&amp;B23&amp;C23&amp;D23&amp;E23&amp;F23&amp;G23&amp;H23&amp;I23&amp;J23&amp;K23</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e22 set value {id:22,text:"使用铁质锹子铲地",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -3964,7 +3963,7 @@
         <v>223</v>
       </c>
       <c r="L24" s="2" t="str">
-        <f>A24&amp;B24&amp;C24&amp;D24&amp;E24&amp;F24&amp;G24&amp;H24&amp;I24&amp;J24&amp;K24</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e23 set value {id:23,text:"使用木质锹子铲地",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4003,7 +4002,7 @@
         <v>223</v>
       </c>
       <c r="L25" s="2" t="str">
-        <f>A25&amp;B25&amp;C25&amp;D25&amp;E25&amp;F25&amp;G25&amp;H25&amp;I25&amp;J25&amp;K25</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e24 set value {id:24,text:"拾取任意按钮(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4030,7 +4029,7 @@
         <v>174</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>175</v>
@@ -4042,8 +4041,8 @@
         <v>223</v>
       </c>
       <c r="L26" s="2" t="str">
-        <f>A26&amp;B26&amp;C26&amp;D26&amp;E26&amp;F26&amp;G26&amp;H26&amp;I26&amp;J26&amp;K26</f>
-        <v>data modify storage ywsj:eventlist args.e25 set value {id:25,text:"食用一个面包",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e25 set value {id:25,text:"食用一个面包",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -4069,7 +4068,7 @@
         <v>174</v>
       </c>
       <c r="H27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>175</v>
@@ -4081,8 +4080,8 @@
         <v>223</v>
       </c>
       <c r="L27" s="2" t="str">
-        <f>A27&amp;B27&amp;C27&amp;D27&amp;E27&amp;F27&amp;G27&amp;H27&amp;I27&amp;J27&amp;K27</f>
-        <v>data modify storage ywsj:eventlist args.e26 set value {id:26,text:"食用一个腐肉",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e26 set value {id:26,text:"食用一个腐肉",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -4108,7 +4107,7 @@
         <v>174</v>
       </c>
       <c r="H28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>175</v>
@@ -4120,8 +4119,8 @@
         <v>223</v>
       </c>
       <c r="L28" s="2" t="str">
-        <f>A28&amp;B28&amp;C28&amp;D28&amp;E28&amp;F28&amp;G28&amp;H28&amp;I28&amp;J28&amp;K28</f>
-        <v>data modify storage ywsj:eventlist args.e27 set value {id:27,text:"食用一个甜浆果",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e27 set value {id:27,text:"食用一个甜浆果",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -4159,7 +4158,7 @@
         <v>223</v>
       </c>
       <c r="L29" s="2" t="str">
-        <f>A29&amp;B29&amp;C29&amp;D29&amp;E29&amp;F29&amp;G29&amp;H29&amp;I29&amp;J29&amp;K29</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e28 set value {id:28,text:"食用一个胡萝卜",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4198,7 +4197,7 @@
         <v>223</v>
       </c>
       <c r="L30" s="2" t="str">
-        <f>A30&amp;B30&amp;C30&amp;D30&amp;E30&amp;F30&amp;G30&amp;H30&amp;I30&amp;J30&amp;K30</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e29 set value {id:29,text:"食用一个烤马铃薯",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4237,7 +4236,7 @@
         <v>223</v>
       </c>
       <c r="L31" s="2" t="str">
-        <f>A31&amp;B31&amp;C31&amp;D31&amp;E31&amp;F31&amp;G31&amp;H31&amp;I31&amp;J31&amp;K31</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e30 set value {id:30,text:"击败一只苦力怕",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4264,7 +4263,7 @@
         <v>174</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>175</v>
@@ -4276,8 +4275,8 @@
         <v>223</v>
       </c>
       <c r="L32" s="2" t="str">
-        <f>A32&amp;B32&amp;C32&amp;D32&amp;E32&amp;F32&amp;G32&amp;H32&amp;I32&amp;J32&amp;K32</f>
-        <v>data modify storage ywsj:eventlist args.e31 set value {id:31,text:"拾取一个草方块(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e31 set value {id:31,text:"拾取一个草方块(需由实体扔出)",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -4315,7 +4314,7 @@
         <v>223</v>
       </c>
       <c r="L33" s="2" t="str">
-        <f>A33&amp;B33&amp;C33&amp;D33&amp;E33&amp;F33&amp;G33&amp;H33&amp;I33&amp;J33&amp;K33</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e32 set value {id:32,text:"拾取一个泥土(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4354,7 +4353,7 @@
         <v>223</v>
       </c>
       <c r="L34" s="2" t="str">
-        <f>A34&amp;B34&amp;C34&amp;D34&amp;E34&amp;F34&amp;G34&amp;H34&amp;I34&amp;J34&amp;K34</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e33 set value {id:33,text:"一次性对玩家造成大于5点的伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4393,7 +4392,7 @@
         <v>223</v>
       </c>
       <c r="L35" s="2" t="str">
-        <f>A35&amp;B35&amp;C35&amp;D35&amp;E35&amp;F35&amp;G35&amp;H35&amp;I35&amp;J35&amp;K35</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e34 set value {id:34,text:"拾取一个沙砾(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4432,7 +4431,7 @@
         <v>223</v>
       </c>
       <c r="L36" s="2" t="str">
-        <f>A36&amp;B36&amp;C36&amp;D36&amp;E36&amp;F36&amp;G36&amp;H36&amp;I36&amp;J36&amp;K36</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e35 set value {id:35,text:"拾取任意一种染料(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4459,7 +4458,7 @@
         <v>174</v>
       </c>
       <c r="H37" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>175</v>
@@ -4471,8 +4470,8 @@
         <v>223</v>
       </c>
       <c r="L37" s="2" t="str">
-        <f>A37&amp;B37&amp;C37&amp;D37&amp;E37&amp;F37&amp;G37&amp;H37&amp;I37&amp;J37&amp;K37</f>
-        <v>data modify storage ywsj:eventlist args.e36 set value {id:36,text:"放置一个草方块",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e36 set value {id:36,text:"放置一个草方块",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -4510,7 +4509,7 @@
         <v>223</v>
       </c>
       <c r="L38" s="2" t="str">
-        <f>A38&amp;B38&amp;C38&amp;D38&amp;E38&amp;F38&amp;G38&amp;H38&amp;I38&amp;J38&amp;K38</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e37 set value {id:37,text:"从主世界穿越到地狱(下届)",difficulty:4,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4549,7 +4548,7 @@
         <v>223</v>
       </c>
       <c r="L39" s="2" t="str">
-        <f>A39&amp;B39&amp;C39&amp;D39&amp;E39&amp;F39&amp;G39&amp;H39&amp;I39&amp;J39&amp;K39</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e38 set value {id:38,text:"从主世界穿越到地末地",difficulty:4,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4588,7 +4587,7 @@
         <v>223</v>
       </c>
       <c r="L40" s="2" t="str">
-        <f>A40&amp;B40&amp;C40&amp;D40&amp;E40&amp;F40&amp;G40&amp;H40&amp;I40&amp;J40&amp;K40</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e39 set value {id:39,text:"从地狱(下届)穿越到主世界",difficulty:4,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4627,7 +4626,7 @@
         <v>223</v>
       </c>
       <c r="L41" s="2" t="str">
-        <f>A41&amp;B41&amp;C41&amp;D41&amp;E41&amp;F41&amp;G41&amp;H41&amp;I41&amp;J41&amp;K41</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e40 set value {id:40,text:"放置一个工作台",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4666,7 +4665,7 @@
         <v>223</v>
       </c>
       <c r="L42" s="2" t="str">
-        <f>A42&amp;B42&amp;C42&amp;D42&amp;E42&amp;F42&amp;G42&amp;H42&amp;I42&amp;J42&amp;K42</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e41 set value {id:41,text:"放置一个圆石台阶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4705,7 +4704,7 @@
         <v>223</v>
       </c>
       <c r="L43" s="2" t="str">
-        <f>A43&amp;B43&amp;C43&amp;D43&amp;E43&amp;F43&amp;G43&amp;H43&amp;I43&amp;J43&amp;K43</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e42 set value {id:42,text:"放置一个圆石墙",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4744,7 +4743,7 @@
         <v>223</v>
       </c>
       <c r="L44" s="2" t="str">
-        <f>A44&amp;B44&amp;C44&amp;D44&amp;E44&amp;F44&amp;G44&amp;H44&amp;I44&amp;J44&amp;K44</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e43 set value {id:43,text:"放置一个煤炭块",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4783,7 +4782,7 @@
         <v>223</v>
       </c>
       <c r="L45" s="2" t="str">
-        <f>A45&amp;B45&amp;C45&amp;D45&amp;E45&amp;F45&amp;G45&amp;H45&amp;I45&amp;J45&amp;K45</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e44 set value {id:44,text:"放置一个黏土块",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4822,7 +4821,7 @@
         <v>223</v>
       </c>
       <c r="L46" s="2" t="str">
-        <f>A46&amp;B46&amp;C46&amp;D46&amp;E46&amp;F46&amp;G46&amp;H46&amp;I46&amp;J46&amp;K46</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e45 set value {id:45,text:"放置一个砂土",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4861,7 +4860,7 @@
         <v>223</v>
       </c>
       <c r="L47" s="2" t="str">
-        <f>A47&amp;B47&amp;C47&amp;D47&amp;E47&amp;F47&amp;G47&amp;H47&amp;I47&amp;J47&amp;K47</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e46 set value {id:46,text:"放置一个红石比较器",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4900,7 +4899,7 @@
         <v>223</v>
       </c>
       <c r="L48" s="2" t="str">
-        <f>A48&amp;B48&amp;C48&amp;D48&amp;E48&amp;F48&amp;G48&amp;H48&amp;I48&amp;J48&amp;K48</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e47 set value {id:47,text:"放置一个堆肥桶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4939,7 +4938,7 @@
         <v>223</v>
       </c>
       <c r="L49" s="2" t="str">
-        <f>A49&amp;B49&amp;C49&amp;D49&amp;E49&amp;F49&amp;G49&amp;H49&amp;I49&amp;J49&amp;K49</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e48 set value {id:48,text:"放置一个铜块",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -4978,7 +4977,7 @@
         <v>223</v>
       </c>
       <c r="L50" s="2" t="str">
-        <f>A50&amp;B50&amp;C50&amp;D50&amp;E50&amp;F50&amp;G50&amp;H50&amp;I50&amp;J50&amp;K50</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e49 set value {id:49,text:"放置一个书架",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5017,7 +5016,7 @@
         <v>223</v>
       </c>
       <c r="L51" s="2" t="str">
-        <f>A51&amp;B51&amp;C51&amp;D51&amp;E51&amp;F51&amp;G51&amp;H51&amp;I51&amp;J51&amp;K51</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e50 set value {id:50,text:"放置任意一种树叶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5056,7 +5055,7 @@
         <v>223</v>
       </c>
       <c r="L52" s="2" t="str">
-        <f>A52&amp;B52&amp;C52&amp;D52&amp;E52&amp;F52&amp;G52&amp;H52&amp;I52&amp;J52&amp;K52</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e51 set value {id:51,text:"放置一个安山岩",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5095,7 +5094,7 @@
         <v>223</v>
       </c>
       <c r="L53" s="2" t="str">
-        <f>A53&amp;B53&amp;C53&amp;D53&amp;E53&amp;F53&amp;G53&amp;H53&amp;I53&amp;J53&amp;K53</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e52 set value {id:52,text:"放置一个安山岩台阶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5134,7 +5133,7 @@
         <v>223</v>
       </c>
       <c r="L54" s="2" t="str">
-        <f>A54&amp;B54&amp;C54&amp;D54&amp;E54&amp;F54&amp;G54&amp;H54&amp;I54&amp;J54&amp;K54</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e53 set value {id:53,text:"放置一个安山岩墙",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5173,7 +5172,7 @@
         <v>223</v>
       </c>
       <c r="L55" s="2" t="str">
-        <f>A55&amp;B55&amp;C55&amp;D55&amp;E55&amp;F55&amp;G55&amp;H55&amp;I55&amp;J55&amp;K55</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e54 set value {id:54,text:"放置一个安山岩楼梯",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5212,7 +5211,7 @@
         <v>223</v>
       </c>
       <c r="L56" s="2" t="str">
-        <f>A56&amp;B56&amp;C56&amp;D56&amp;E56&amp;F56&amp;G56&amp;H56&amp;I56&amp;J56&amp;K56</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e55 set value {id:55,text:"放置一个铁砧",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5251,7 +5250,7 @@
         <v>223</v>
       </c>
       <c r="L57" s="2" t="str">
-        <f>A57&amp;B57&amp;C57&amp;D57&amp;E57&amp;F57&amp;G57&amp;H57&amp;I57&amp;J57&amp;K57</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e56 set value {id:56,text:"放置一个木桶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5290,7 +5289,7 @@
         <v>223</v>
       </c>
       <c r="L58" s="2" t="str">
-        <f>A58&amp;B58&amp;C58&amp;D58&amp;E58&amp;F58&amp;G58&amp;H58&amp;I58&amp;J58&amp;K58</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e57 set value {id:57,text:"放置一个玄武岩",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5329,7 +5328,7 @@
         <v>223</v>
       </c>
       <c r="L59" s="2" t="str">
-        <f>A59&amp;B59&amp;C59&amp;D59&amp;E59&amp;F59&amp;G59&amp;H59&amp;I59&amp;J59&amp;K59</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e58 set value {id:58,text:"放置一个营火",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5368,7 +5367,7 @@
         <v>223</v>
       </c>
       <c r="L60" s="2" t="str">
-        <f>A60&amp;B60&amp;C60&amp;D60&amp;E60&amp;F60&amp;G60&amp;H60&amp;I60&amp;J60&amp;K60</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e59 set value {id:59,text:"放置一个钟",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5407,7 +5406,7 @@
         <v>223</v>
       </c>
       <c r="L61" s="2" t="str">
-        <f>A61&amp;B61&amp;C61&amp;D61&amp;E61&amp;F61&amp;G61&amp;H61&amp;I61&amp;J61&amp;K61</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e60 set value {id:60,text:"放置任意一种告示牌",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5434,7 +5433,7 @@
         <v>174</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>175</v>
@@ -5446,8 +5445,8 @@
         <v>223</v>
       </c>
       <c r="L62" s="2" t="str">
-        <f>A62&amp;B62&amp;C62&amp;D62&amp;E62&amp;F62&amp;G62&amp;H62&amp;I62&amp;J62&amp;K62</f>
-        <v>data modify storage ywsj:eventlist args.e61 set value {id:61,text:"种下任意一种树苗",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="0"/>
+        <v>data modify storage ywsj:eventlist args.e61 set value {id:61,text:"种下任意一种树苗",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -5485,7 +5484,7 @@
         <v>223</v>
       </c>
       <c r="L63" s="2" t="str">
-        <f>A63&amp;B63&amp;C63&amp;D63&amp;E63&amp;F63&amp;G63&amp;H63&amp;I63&amp;J63&amp;K63</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e62 set value {id:62,text:"放置任意一种木门",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5524,7 +5523,7 @@
         <v>223</v>
       </c>
       <c r="L64" s="2" t="str">
-        <f>A64&amp;B64&amp;C64&amp;D64&amp;E64&amp;F64&amp;G64&amp;H64&amp;I64&amp;J64&amp;K64</f>
+        <f t="shared" si="0"/>
         <v>data modify storage ywsj:eventlist args.e63 set value {id:63,text:"放置任意一种门",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5563,7 +5562,7 @@
         <v>223</v>
       </c>
       <c r="L65" s="2" t="str">
-        <f>A65&amp;B65&amp;C65&amp;D65&amp;E65&amp;F65&amp;G65&amp;H65&amp;I65&amp;J65&amp;K65</f>
+        <f t="shared" ref="L65:L128" si="1">A65&amp;B65&amp;C65&amp;D65&amp;E65&amp;F65&amp;G65&amp;H65&amp;I65&amp;J65&amp;K65</f>
         <v>data modify storage ywsj:eventlist args.e64 set value {id:64,text:"放置一个铁门",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5602,7 +5601,7 @@
         <v>223</v>
       </c>
       <c r="L66" s="2" t="str">
-        <f>A66&amp;B66&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;H66&amp;I66&amp;J66&amp;K66</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e65 set value {id:65,text:"放置任意一种木质台阶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5641,7 +5640,7 @@
         <v>223</v>
       </c>
       <c r="L67" s="2" t="str">
-        <f>A67&amp;B67&amp;C67&amp;D67&amp;E67&amp;F67&amp;G67&amp;H67&amp;I67&amp;J67&amp;K67</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e66 set value {id:66,text:"放置任意一种台阶",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5668,7 +5667,7 @@
         <v>174</v>
       </c>
       <c r="H68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>175</v>
@@ -5680,8 +5679,8 @@
         <v>223</v>
       </c>
       <c r="L68" s="2" t="str">
-        <f>A68&amp;B68&amp;C68&amp;D68&amp;E68&amp;F68&amp;G68&amp;H68&amp;I68&amp;J68&amp;K68</f>
-        <v>data modify storage ywsj:eventlist args.e67 set value {id:67,text:"放置任意一种羊毛地毯",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="1"/>
+        <v>data modify storage ywsj:eventlist args.e67 set value {id:67,text:"放置任意一种羊毛地毯",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -5719,7 +5718,7 @@
         <v>223</v>
       </c>
       <c r="L69" s="2" t="str">
-        <f>A69&amp;B69&amp;C69&amp;D69&amp;E69&amp;F69&amp;G69&amp;H69&amp;I69&amp;J69&amp;K69</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e68 set value {id:68,text:"放置一个黑石",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5758,7 +5757,7 @@
         <v>223</v>
       </c>
       <c r="L70" s="2" t="str">
-        <f>A70&amp;B70&amp;C70&amp;D70&amp;E70&amp;F70&amp;G70&amp;H70&amp;I70&amp;J70&amp;K70</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e69 set value {id:69,text:"种下任意一束花",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5797,7 +5796,7 @@
         <v>223</v>
       </c>
       <c r="L71" s="2" t="str">
-        <f>A71&amp;B71&amp;C71&amp;D71&amp;E71&amp;F71&amp;G71&amp;H71&amp;I71&amp;J71&amp;K71</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e70 set value {id:70,text:"种下任意一束高丛花",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5836,7 +5835,7 @@
         <v>223</v>
       </c>
       <c r="L72" s="2" t="str">
-        <f>A72&amp;B72&amp;C72&amp;D72&amp;E72&amp;F72&amp;G72&amp;H72&amp;I72&amp;J72&amp;K72</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e71 set value {id:71,text:"种下任意一束低丛花",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5875,7 +5874,7 @@
         <v>223</v>
       </c>
       <c r="L73" s="2" t="str">
-        <f>A73&amp;B73&amp;C73&amp;D73&amp;E73&amp;F73&amp;G73&amp;H73&amp;I73&amp;J73&amp;K73</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e72 set value {id:72,text:"放置一个酿造台",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5914,7 +5913,7 @@
         <v>223</v>
       </c>
       <c r="L74" s="2" t="str">
-        <f>A74&amp;B74&amp;C74&amp;D74&amp;E74&amp;F74&amp;G74&amp;H74&amp;I74&amp;J74&amp;K74</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e73 set value {id:73,text:"玩家被远程射中",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5953,7 +5952,7 @@
         <v>223</v>
       </c>
       <c r="L75" s="2" t="str">
-        <f>A75&amp;B75&amp;C75&amp;D75&amp;E75&amp;F75&amp;G75&amp;H75&amp;I75&amp;J75&amp;K75</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e74 set value {id:74,text:"对自己造成爆炸伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -5992,7 +5991,7 @@
         <v>223</v>
       </c>
       <c r="L76" s="2" t="str">
-        <f>A76&amp;B76&amp;C76&amp;D76&amp;E76&amp;F76&amp;G76&amp;H76&amp;I76&amp;J76&amp;K76</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e75 set value {id:75,text:"对自己造成溺水伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6031,7 +6030,7 @@
         <v>223</v>
       </c>
       <c r="L77" s="2" t="str">
-        <f>A77&amp;B77&amp;C77&amp;D77&amp;E77&amp;F77&amp;G77&amp;H77&amp;I77&amp;J77&amp;K77</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e76 set value {id:76,text:"对自己造成摔落伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6070,7 +6069,7 @@
         <v>223</v>
       </c>
       <c r="L78" s="2" t="str">
-        <f>A78&amp;B78&amp;C78&amp;D78&amp;E78&amp;F78&amp;G78&amp;H78&amp;I78&amp;J78&amp;K78</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e77 set value {id:77,text:"对自己造成魔法伤害",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6109,7 +6108,7 @@
         <v>223</v>
       </c>
       <c r="L79" s="2" t="str">
-        <f>A79&amp;B79&amp;C79&amp;D79&amp;E79&amp;F79&amp;G79&amp;H79&amp;I79&amp;J79&amp;K79</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e78 set value {id:78,text:"对自己造成无视护甲穿甲伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6148,7 +6147,7 @@
         <v>223</v>
       </c>
       <c r="L80" s="2" t="str">
-        <f>A80&amp;B80&amp;C80&amp;D80&amp;E80&amp;F80&amp;G80&amp;H80&amp;I80&amp;J80&amp;K80</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e79 set value {id:79,text:"对自己造成一次性不大于5点的伤害",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6175,7 +6174,7 @@
         <v>174</v>
       </c>
       <c r="H81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>175</v>
@@ -6187,8 +6186,8 @@
         <v>223</v>
       </c>
       <c r="L81" s="2" t="str">
-        <f>A81&amp;B81&amp;C81&amp;D81&amp;E81&amp;F81&amp;G81&amp;H81&amp;I81&amp;J81&amp;K81</f>
-        <v>data modify storage ywsj:eventlist args.e80 set value {id:80,text:"拾取一张白纸(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="1"/>
+        <v>data modify storage ywsj:eventlist args.e80 set value {id:80,text:"拾取一张白纸(需由实体扔出)",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -6226,7 +6225,7 @@
         <v>223</v>
       </c>
       <c r="L82" s="2" t="str">
-        <f>A82&amp;B82&amp;C82&amp;D82&amp;E82&amp;F82&amp;G82&amp;H82&amp;I82&amp;J82&amp;K82</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e81 set value {id:81,text:"站在草方块上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6265,7 +6264,7 @@
         <v>223</v>
       </c>
       <c r="L83" s="2" t="str">
-        <f>A83&amp;B83&amp;C83&amp;D83&amp;E83&amp;F83&amp;G83&amp;H83&amp;I83&amp;J83&amp;K83</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e82 set value {id:82,text:"站在石头上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6304,7 +6303,7 @@
         <v>223</v>
       </c>
       <c r="L84" s="2" t="str">
-        <f>A84&amp;B84&amp;C84&amp;D84&amp;E84&amp;F84&amp;G84&amp;H84&amp;I84&amp;J84&amp;K84</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e83 set value {id:83,text:"站在圆石上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6343,7 +6342,7 @@
         <v>223</v>
       </c>
       <c r="L85" s="2" t="str">
-        <f>A85&amp;B85&amp;C85&amp;D85&amp;E85&amp;F85&amp;G85&amp;H85&amp;I85&amp;J85&amp;K85</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e84 set value {id:84,text:"站在任意树叶上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6382,7 +6381,7 @@
         <v>223</v>
       </c>
       <c r="L86" s="2" t="str">
-        <f>A86&amp;B86&amp;C86&amp;D86&amp;E86&amp;F86&amp;G86&amp;H86&amp;I86&amp;J86&amp;K86</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e85 set value {id:85,text:"站在泥土上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6421,7 +6420,7 @@
         <v>223</v>
       </c>
       <c r="L87" s="2" t="str">
-        <f>A87&amp;B87&amp;C87&amp;D87&amp;E87&amp;F87&amp;G87&amp;H87&amp;I87&amp;J87&amp;K87</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e86 set value {id:86,text:"站在沙子上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6460,7 +6459,7 @@
         <v>223</v>
       </c>
       <c r="L88" s="2" t="str">
-        <f>A88&amp;B88&amp;C88&amp;D88&amp;E88&amp;F88&amp;G88&amp;H88&amp;I88&amp;J88&amp;K88</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e87 set value {id:87,text:"站在粘土块上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6499,7 +6498,7 @@
         <v>223</v>
       </c>
       <c r="L89" s="2" t="str">
-        <f>A89&amp;B89&amp;C89&amp;D89&amp;E89&amp;F89&amp;G89&amp;H89&amp;I89&amp;J89&amp;K89</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e88 set value {id:88,text:"站在苔藓块上",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6538,7 +6537,7 @@
         <v>223</v>
       </c>
       <c r="L90" s="2" t="str">
-        <f>A90&amp;B90&amp;C90&amp;D90&amp;E90&amp;F90&amp;G90&amp;H90&amp;I90&amp;J90&amp;K90</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e89 set value {id:89,text:"站在橡木木板上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6577,7 +6576,7 @@
         <v>223</v>
       </c>
       <c r="L91" s="2" t="str">
-        <f>A91&amp;B91&amp;C91&amp;D91&amp;E91&amp;F91&amp;G91&amp;H91&amp;I91&amp;J91&amp;K91</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e90 set value {id:90,text:"站在雪块上",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6616,7 +6615,7 @@
         <v>223</v>
       </c>
       <c r="L92" s="2" t="str">
-        <f>A92&amp;B92&amp;C92&amp;D92&amp;E92&amp;F92&amp;G92&amp;H92&amp;I92&amp;J92&amp;K92</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e91 set value {id:91,text:"站在床上",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6655,7 +6654,7 @@
         <v>223</v>
       </c>
       <c r="L93" s="2" t="str">
-        <f>A93&amp;B93&amp;C93&amp;D93&amp;E93&amp;F93&amp;G93&amp;H93&amp;I93&amp;J93&amp;K93</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e92 set value {id:92,text:"击败一只鸡",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6694,7 +6693,7 @@
         <v>223</v>
       </c>
       <c r="L94" s="2" t="str">
-        <f>A94&amp;B94&amp;C94&amp;D94&amp;E94&amp;F94&amp;G94&amp;H94&amp;I94&amp;J94&amp;K94</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e93 set value {id:93,text:"击败一只牛",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6733,7 +6732,7 @@
         <v>223</v>
       </c>
       <c r="L95" s="2" t="str">
-        <f>A95&amp;B95&amp;C95&amp;D95&amp;E95&amp;F95&amp;G95&amp;H95&amp;I95&amp;J95&amp;K95</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e94 set value {id:94,text:"击败一只猪",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6772,7 +6771,7 @@
         <v>223</v>
       </c>
       <c r="L96" s="2" t="str">
-        <f>A96&amp;B96&amp;C96&amp;D96&amp;E96&amp;F96&amp;G96&amp;H96&amp;I96&amp;J96&amp;K96</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e95 set value {id:95,text:"击败一只绵羊",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6811,7 +6810,7 @@
         <v>223</v>
       </c>
       <c r="L97" s="2" t="str">
-        <f>A97&amp;B97&amp;C97&amp;D97&amp;E97&amp;F97&amp;G97&amp;H97&amp;I97&amp;J97&amp;K97</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e96 set value {id:96,text:"击败一只村民",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6850,7 +6849,7 @@
         <v>223</v>
       </c>
       <c r="L98" s="2" t="str">
-        <f>A98&amp;B98&amp;C98&amp;D98&amp;E98&amp;F98&amp;G98&amp;H98&amp;I98&amp;J98&amp;K98</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e97 set value {id:97,text:"击败一只鳕鱼",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6889,7 +6888,7 @@
         <v>223</v>
       </c>
       <c r="L99" s="2" t="str">
-        <f>A99&amp;B99&amp;C99&amp;D99&amp;E99&amp;F99&amp;G99&amp;H99&amp;I99&amp;J99&amp;K99</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e98 set value {id:98,text:"击败一只鲑鱼",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6928,7 +6927,7 @@
         <v>223</v>
       </c>
       <c r="L100" s="2" t="str">
-        <f>A100&amp;B100&amp;C100&amp;D100&amp;E100&amp;F100&amp;G100&amp;H100&amp;I100&amp;J100&amp;K100</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e99 set value {id:99,text:"击败一只马",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -6967,7 +6966,7 @@
         <v>223</v>
       </c>
       <c r="L101" s="2" t="str">
-        <f>A101&amp;B101&amp;C101&amp;D101&amp;E101&amp;F101&amp;G101&amp;H101&amp;I101&amp;J101&amp;K101</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e100 set value {id:100,text:"击败一只驴",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7006,7 +7005,7 @@
         <v>223</v>
       </c>
       <c r="L102" s="2" t="str">
-        <f>A102&amp;B102&amp;C102&amp;D102&amp;E102&amp;F102&amp;G102&amp;H102&amp;I102&amp;J102&amp;K102</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e101 set value {id:101,text:"击败一只骡",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7045,7 +7044,7 @@
         <v>223</v>
       </c>
       <c r="L103" s="2" t="str">
-        <f>A103&amp;B103&amp;C103&amp;D103&amp;E103&amp;F103&amp;G103&amp;H103&amp;I103&amp;J103&amp;K103</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e102 set value {id:102,text:"击败一只鱿鱼",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7084,7 +7083,7 @@
         <v>223</v>
       </c>
       <c r="L104" s="2" t="str">
-        <f>A104&amp;B104&amp;C104&amp;D104&amp;E104&amp;F104&amp;G104&amp;H104&amp;I104&amp;J104&amp;K104</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e103 set value {id:103,text:"击败一只河豚",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7123,7 +7122,7 @@
         <v>223</v>
       </c>
       <c r="L105" s="2" t="str">
-        <f>A105&amp;B105&amp;C105&amp;D105&amp;E105&amp;F105&amp;G105&amp;H105&amp;I105&amp;J105&amp;K105</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e104 set value {id:104,text:"击败一只铁傀儡",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7162,7 +7161,7 @@
         <v>223</v>
       </c>
       <c r="L106" s="2" t="str">
-        <f>A106&amp;B106&amp;C106&amp;D106&amp;E106&amp;F106&amp;G106&amp;H106&amp;I106&amp;J106&amp;K106</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e105 set value {id:105,text:"击败一只狼",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7201,7 +7200,7 @@
         <v>223</v>
       </c>
       <c r="L107" s="2" t="str">
-        <f>A107&amp;B107&amp;C107&amp;D107&amp;E107&amp;F107&amp;G107&amp;H107&amp;I107&amp;J107&amp;K107</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e106 set value {id:106,text:"击败一只溺尸",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7240,7 +7239,7 @@
         <v>223</v>
       </c>
       <c r="L108" s="2" t="str">
-        <f>A108&amp;B108&amp;C108&amp;D108&amp;E108&amp;F108&amp;G108&amp;H108&amp;I108&amp;J108&amp;K108</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e107 set value {id:107,text:"击败一只尸壳",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7279,7 +7278,7 @@
         <v>223</v>
       </c>
       <c r="L109" s="2" t="str">
-        <f>A109&amp;B109&amp;C109&amp;D109&amp;E109&amp;F109&amp;G109&amp;H109&amp;I109&amp;J109&amp;K109</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e108 set value {id:108,text:"击败一只骷髅",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7318,7 +7317,7 @@
         <v>223</v>
       </c>
       <c r="L110" s="2" t="str">
-        <f>A110&amp;B110&amp;C110&amp;D110&amp;E110&amp;F110&amp;G110&amp;H110&amp;I110&amp;J110&amp;K110</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e109 set value {id:109,text:"击败一只女巫",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7357,7 +7356,7 @@
         <v>223</v>
       </c>
       <c r="L111" s="2" t="str">
-        <f>A111&amp;B111&amp;C111&amp;D111&amp;E111&amp;F111&amp;G111&amp;H111&amp;I111&amp;J111&amp;K111</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e110 set value {id:110,text:"击败一只史莱姆",difficulty:2,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7396,7 +7395,7 @@
         <v>223</v>
       </c>
       <c r="L112" s="2" t="str">
-        <f>A112&amp;B112&amp;C112&amp;D112&amp;E112&amp;F112&amp;G112&amp;H112&amp;I112&amp;J112&amp;K112</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e111 set value {id:111,text:"击败一只僵尸村民",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7435,7 +7434,7 @@
         <v>223</v>
       </c>
       <c r="L113" s="2" t="str">
-        <f>A113&amp;B113&amp;C113&amp;D113&amp;E113&amp;F113&amp;G113&amp;H113&amp;I113&amp;J113&amp;K113</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e112 set value {id:112,text:"击败一只蜘蛛",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7462,7 +7461,7 @@
         <v>174</v>
       </c>
       <c r="H114" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>175</v>
@@ -7474,8 +7473,8 @@
         <v>223</v>
       </c>
       <c r="L114" s="2" t="str">
-        <f>A114&amp;B114&amp;C114&amp;D114&amp;E114&amp;F114&amp;G114&amp;H114&amp;I114&amp;J114&amp;K114</f>
-        <v>data modify storage ywsj:eventlist args.e113 set value {id:113,text:"击败一个玩家",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
+        <f t="shared" si="1"/>
+        <v>data modify storage ywsj:eventlist args.e113 set value {id:113,text:"击败一个玩家",difficulty:3,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
@@ -7513,7 +7512,7 @@
         <v>223</v>
       </c>
       <c r="L115" s="2" t="str">
-        <f>A115&amp;B115&amp;C115&amp;D115&amp;E115&amp;F115&amp;G115&amp;H115&amp;I115&amp;J115&amp;K115</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e114 set value {id:114,text:"潜行移动5距离",difficulty:1,criteria:"minecraft.custom:minecraft.crouch_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7552,7 +7551,7 @@
         <v>223</v>
       </c>
       <c r="L116" s="2" t="str">
-        <f>A116&amp;B116&amp;C116&amp;D116&amp;E116&amp;F116&amp;G116&amp;H116&amp;I116&amp;J116&amp;K116</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e115 set value {id:115,text:"摔落3距离",difficulty:1,criteria:"minecraft.custom:minecraft.fall_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7591,7 +7590,7 @@
         <v>223</v>
       </c>
       <c r="L117" s="2" t="str">
-        <f>A117&amp;B117&amp;C117&amp;D117&amp;E117&amp;F117&amp;G117&amp;H117&amp;I117&amp;J117&amp;K117</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e116 set value {id:116,text:"打开1次木桶",difficulty:1,criteria:"minecraft.custom:minecraft.open_barrel",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7630,7 +7629,7 @@
         <v>223</v>
       </c>
       <c r="L118" s="2" t="str">
-        <f>A118&amp;B118&amp;C118&amp;D118&amp;E118&amp;F118&amp;G118&amp;H118&amp;I118&amp;J118&amp;K118</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e117 set value {id:117,text:"打开30次木桶",difficulty:1,criteria:"minecraft.custom:minecraft.open_barrel",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7669,7 +7668,7 @@
         <v>223</v>
       </c>
       <c r="L119" s="2" t="str">
-        <f>A119&amp;B119&amp;C119&amp;D119&amp;E119&amp;F119&amp;G119&amp;H119&amp;I119&amp;J119&amp;K119</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e118 set value {id:118,text:"造成的伤害总量大于5",difficulty:1,criteria:"minecraft.custom:minecraft.damage_dealt",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7708,7 +7707,7 @@
         <v>223</v>
       </c>
       <c r="L120" s="2" t="str">
-        <f>A120&amp;B120&amp;C120&amp;D120&amp;E120&amp;F120&amp;G120&amp;H120&amp;I120&amp;J120&amp;K120</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e119 set value {id:119,text:"敲5次钟",difficulty:2,criteria:"minecraft.custom:minecraft.bell_ring",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7747,7 +7746,7 @@
         <v>223</v>
       </c>
       <c r="L121" s="2" t="str">
-        <f>A121&amp;B121&amp;C121&amp;D121&amp;E121&amp;F121&amp;G121&amp;H121&amp;I121&amp;J121&amp;K121</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e120 set value {id:120,text:"打开5次箱子",difficulty:1,criteria:"minecraft.custom:minecraft.open_chest",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7786,7 +7785,7 @@
         <v>223</v>
       </c>
       <c r="L122" s="2" t="str">
-        <f>A122&amp;B122&amp;C122&amp;D122&amp;E122&amp;F122&amp;G122&amp;H122&amp;I122&amp;J122&amp;K122</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e121 set value {id:121,text:"打开60次箱子",difficulty:1,criteria:"minecraft.custom:minecraft.open_chest",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7825,7 +7824,7 @@
         <v>223</v>
       </c>
       <c r="L123" s="2" t="str">
-        <f>A123&amp;B123&amp;C123&amp;D123&amp;E123&amp;F123&amp;G123&amp;H123&amp;I123&amp;J123&amp;K123</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e122 set value {id:122,text:"坐船移动20距离",difficulty:1,criteria:"minecraft.custom:minecraft.boat_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7864,7 +7863,7 @@
         <v>223</v>
       </c>
       <c r="L124" s="2" t="str">
-        <f>A124&amp;B124&amp;C124&amp;D124&amp;E124&amp;F124&amp;G124&amp;H124&amp;I124&amp;J124&amp;K124</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e123 set value {id:123,text:"骑马移动5距离",difficulty:3,criteria:"minecraft.custom:minecraft.horse_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7903,7 +7902,7 @@
         <v>223</v>
       </c>
       <c r="L125" s="2" t="str">
-        <f>A125&amp;B125&amp;C125&amp;D125&amp;E125&amp;F125&amp;G125&amp;H125&amp;I125&amp;J125&amp;K125</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e124 set value {id:124,text:"攀爬10距离",difficulty:1,criteria:"minecraft.custom:minecraft.climb_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -7930,7 +7929,7 @@
         <v>174</v>
       </c>
       <c r="H126" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>175</v>
@@ -7942,8 +7941,8 @@
         <v>223</v>
       </c>
       <c r="L126" s="2" t="str">
-        <f>A126&amp;B126&amp;C126&amp;D126&amp;E126&amp;F126&amp;G126&amp;H126&amp;I126&amp;J126&amp;K126</f>
-        <v>data modify storage ywsj:eventlist args.e125 set value {id:125,text:"飞行10距离",difficulty:3,criteria:"minecraft.custom:minecraft.fly_one_cm",args:{onlycheck:0}}</v>
+        <f t="shared" si="1"/>
+        <v>data modify storage ywsj:eventlist args.e125 set value {id:125,text:"飞行10距离",difficulty:2,criteria:"minecraft.custom:minecraft.fly_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
@@ -7981,7 +7980,7 @@
         <v>223</v>
       </c>
       <c r="L127" s="2" t="str">
-        <f>A127&amp;B127&amp;C127&amp;D127&amp;E127&amp;F127&amp;G127&amp;H127&amp;I127&amp;J127&amp;K127</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e126 set value {id:126,text:"疾跑10距离",difficulty:1,criteria:"minecraft.custom:minecraft.sprint_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8020,7 +8019,7 @@
         <v>223</v>
       </c>
       <c r="L128" s="2" t="str">
-        <f>A128&amp;B128&amp;C128&amp;D128&amp;E128&amp;F128&amp;G128&amp;H128&amp;I128&amp;J128&amp;K128</f>
+        <f t="shared" si="1"/>
         <v>data modify storage ywsj:eventlist args.e127 set value {id:127,text:"疾跑50距离",difficulty:1,criteria:"minecraft.custom:minecraft.sprint_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8059,7 +8058,7 @@
         <v>223</v>
       </c>
       <c r="L129" s="2" t="str">
-        <f>A129&amp;B129&amp;C129&amp;D129&amp;E129&amp;F129&amp;G129&amp;H129&amp;I129&amp;J129&amp;K129</f>
+        <f t="shared" ref="L129:L192" si="2">A129&amp;B129&amp;C129&amp;D129&amp;E129&amp;F129&amp;G129&amp;H129&amp;I129&amp;J129&amp;K129</f>
         <v>data modify storage ywsj:eventlist args.e128 set value {id:128,text:"疾跑100距离",difficulty:1,criteria:"minecraft.custom:minecraft.sprint_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8098,7 +8097,7 @@
         <v>223</v>
       </c>
       <c r="L130" s="2" t="str">
-        <f>A130&amp;B130&amp;C130&amp;D130&amp;E130&amp;F130&amp;G130&amp;H130&amp;I130&amp;J130&amp;K130</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e129 set value {id:129,text:"游泳20距离",difficulty:1,criteria:"minecraft.custom:minecraft.swim_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8137,7 +8136,7 @@
         <v>223</v>
       </c>
       <c r="L131" s="2" t="str">
-        <f>A131&amp;B131&amp;C131&amp;D131&amp;E131&amp;F131&amp;G131&amp;H131&amp;I131&amp;J131&amp;K131</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e130 set value {id:130,text:"游泳50距离",difficulty:1,criteria:"minecraft.custom:minecraft.swim_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8176,7 +8175,7 @@
         <v>223</v>
       </c>
       <c r="L132" s="2" t="str">
-        <f>A132&amp;B132&amp;C132&amp;D132&amp;E132&amp;F132&amp;G132&amp;H132&amp;I132&amp;J132&amp;K132</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e131 set value {id:131,text:"30内不死亡",difficulty:1,criteria:"minecraft.custom:minecraft.time_since_death",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8215,7 +8214,7 @@
         <v>223</v>
       </c>
       <c r="L133" s="2" t="str">
-        <f>A133&amp;B133&amp;C133&amp;D133&amp;E133&amp;F133&amp;G133&amp;H133&amp;I133&amp;J133&amp;K133</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e132 set value {id:132,text:"与村民交互1次",difficulty:2,criteria:"minecraft.custom:minecraft.talked_to_villager",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8254,7 +8253,7 @@
         <v>223</v>
       </c>
       <c r="L134" s="2" t="str">
-        <f>A134&amp;B134&amp;C134&amp;D134&amp;E134&amp;F134&amp;G134&amp;H134&amp;I134&amp;J134&amp;K134</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e133 set value {id:133,text:"击杀任意5个生物",difficulty:1,criteria:"minecraft.custom:minecraft.mob_kills",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8293,7 +8292,7 @@
         <v>223</v>
       </c>
       <c r="L135" s="2" t="str">
-        <f>A135&amp;B135&amp;C135&amp;D135&amp;E135&amp;F135&amp;G135&amp;H135&amp;I135&amp;J135&amp;K135</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e134 set value {id:134,text:"跳跃10次",difficulty:1,criteria:"minecraft.custom:minecraft.jump",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8332,7 +8331,7 @@
         <v>223</v>
       </c>
       <c r="L136" s="2" t="str">
-        <f>A136&amp;B136&amp;C136&amp;D136&amp;E136&amp;F136&amp;G136&amp;H136&amp;I136&amp;J136&amp;K136</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e135 set value {id:135,text:"跳跃30次",difficulty:1,criteria:"minecraft.custom:minecraft.jump",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8371,7 +8370,7 @@
         <v>223</v>
       </c>
       <c r="L137" s="2" t="str">
-        <f>A137&amp;B137&amp;C137&amp;D137&amp;E137&amp;F137&amp;G137&amp;H137&amp;I137&amp;J137&amp;K137</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e136 set value {id:136,text:"与工作台交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_crafting_table",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8410,7 +8409,7 @@
         <v>223</v>
       </c>
       <c r="L138" s="2" t="str">
-        <f>A138&amp;B138&amp;C138&amp;D138&amp;E138&amp;F138&amp;G138&amp;H138&amp;I138&amp;J138&amp;K138</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e137 set value {id:137,text:"与工作台交互10次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_crafting_table",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8449,7 +8448,7 @@
         <v>223</v>
       </c>
       <c r="L139" s="2" t="str">
-        <f>A139&amp;B139&amp;C139&amp;D139&amp;E139&amp;F139&amp;G139&amp;H139&amp;I139&amp;J139&amp;K139</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e138 set value {id:138,text:"与熔炉交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_furnace",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8488,7 +8487,7 @@
         <v>223</v>
       </c>
       <c r="L140" s="2" t="str">
-        <f>A140&amp;B140&amp;C140&amp;D140&amp;E140&amp;F140&amp;G140&amp;H140&amp;I140&amp;J140&amp;K140</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e139 set value {id:139,text:"与熔炉交互3次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_furnace",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8527,7 +8526,7 @@
         <v>223</v>
       </c>
       <c r="L141" s="2" t="str">
-        <f>A141&amp;B141&amp;C141&amp;D141&amp;E141&amp;F141&amp;G141&amp;H141&amp;I141&amp;J141&amp;K141</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e140 set value {id:140,text:"与发射器交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.inspect_dispenser",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8566,7 +8565,7 @@
         <v>223</v>
       </c>
       <c r="L142" s="2" t="str">
-        <f>A142&amp;B142&amp;C142&amp;D142&amp;E142&amp;F142&amp;G142&amp;H142&amp;I142&amp;J142&amp;K142</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e141 set value {id:141,text:"与投掷器交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.inspect_dropper",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8605,7 +8604,7 @@
         <v>223</v>
       </c>
       <c r="L143" s="2" t="str">
-        <f>A143&amp;B143&amp;C143&amp;D143&amp;E143&amp;F143&amp;G143&amp;H143&amp;I143&amp;J143&amp;K143</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e142 set value {id:142,text:"与末影箱交互1次",difficulty:3,criteria:"minecraft.custom:minecraft.open_enderchest",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8644,7 +8643,7 @@
         <v>223</v>
       </c>
       <c r="L144" s="2" t="str">
-        <f>A144&amp;B144&amp;C144&amp;D144&amp;E144&amp;F144&amp;G144&amp;H144&amp;I144&amp;J144&amp;K144</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e143 set value {id:143,text:"与漏斗交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.inspect_hopper",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8683,7 +8682,7 @@
         <v>223</v>
       </c>
       <c r="L145" s="2" t="str">
-        <f>A145&amp;B145&amp;C145&amp;D145&amp;E145&amp;F145&amp;G145&amp;H145&amp;I145&amp;J145&amp;K145</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e144 set value {id:144,text:"与铁砧交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_anvil",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8722,7 +8721,7 @@
         <v>223</v>
       </c>
       <c r="L146" s="2" t="str">
-        <f>A146&amp;B146&amp;C146&amp;D146&amp;E146&amp;F146&amp;G146&amp;H146&amp;I146&amp;J146&amp;K146</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e145 set value {id:145,text:"与高炉交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_blast_furnace",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8761,7 +8760,7 @@
         <v>223</v>
       </c>
       <c r="L147" s="2" t="str">
-        <f>A147&amp;B147&amp;C147&amp;D147&amp;E147&amp;F147&amp;G147&amp;H147&amp;I147&amp;J147&amp;K147</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e146 set value {id:146,text:"与酿造台交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_brewingstand",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8800,7 +8799,7 @@
         <v>223</v>
       </c>
       <c r="L148" s="2" t="str">
-        <f>A148&amp;B148&amp;C148&amp;D148&amp;E148&amp;F148&amp;G148&amp;H148&amp;I148&amp;J148&amp;K148</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e147 set value {id:147,text:"与营火交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_campfire",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8839,7 +8838,7 @@
         <v>223</v>
       </c>
       <c r="L149" s="2" t="str">
-        <f>A149&amp;B149&amp;C149&amp;D149&amp;E149&amp;F149&amp;G149&amp;H149&amp;I149&amp;J149&amp;K149</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e148 set value {id:148,text:"与制图台交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_cartography_table",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8878,7 +8877,7 @@
         <v>223</v>
       </c>
       <c r="L150" s="2" t="str">
-        <f>A150&amp;B150&amp;C150&amp;D150&amp;E150&amp;F150&amp;G150&amp;H150&amp;I150&amp;J150&amp;K150</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e149 set value {id:149,text:"与砂轮交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_grindstone",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8917,7 +8916,7 @@
         <v>223</v>
       </c>
       <c r="L151" s="2" t="str">
-        <f>A151&amp;B151&amp;C151&amp;D151&amp;E151&amp;F151&amp;G151&amp;H151&amp;I151&amp;J151&amp;K151</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e150 set value {id:150,text:"与讲台交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_lectern",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8956,7 +8955,7 @@
         <v>223</v>
       </c>
       <c r="L152" s="2" t="str">
-        <f>A152&amp;B152&amp;C152&amp;D152&amp;E152&amp;F152&amp;G152&amp;H152&amp;I152&amp;J152&amp;K152</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e151 set value {id:151,text:"与织布机交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_loom",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -8995,7 +8994,7 @@
         <v>223</v>
       </c>
       <c r="L153" s="2" t="str">
-        <f>A153&amp;B153&amp;C153&amp;D153&amp;E153&amp;F153&amp;G153&amp;H153&amp;I153&amp;J153&amp;K153</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e152 set value {id:152,text:"与锻造台交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_smithing_table",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9034,7 +9033,7 @@
         <v>223</v>
       </c>
       <c r="L154" s="2" t="str">
-        <f>A154&amp;B154&amp;C154&amp;D154&amp;E154&amp;F154&amp;G154&amp;H154&amp;I154&amp;J154&amp;K154</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e153 set value {id:153,text:"与烟熏炉交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_smoker",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9073,7 +9072,7 @@
         <v>223</v>
       </c>
       <c r="L155" s="2" t="str">
-        <f>A155&amp;B155&amp;C155&amp;D155&amp;E155&amp;F155&amp;G155&amp;H155&amp;I155&amp;J155&amp;K155</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e154 set value {id:154,text:"与切石机交互1次",difficulty:1,criteria:"minecraft.custom:minecraft.interact_with_stonecutter",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9112,7 +9111,7 @@
         <v>223</v>
       </c>
       <c r="L156" s="2" t="str">
-        <f>A156&amp;B156&amp;C156&amp;D156&amp;E156&amp;F156&amp;G156&amp;H156&amp;I156&amp;J156&amp;K156</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e155 set value {id:155,text:"将任意植物种进花盆",difficulty:1,criteria:"minecraft.crafted:light_weighted_pressure_plate",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9151,7 +9150,7 @@
         <v>223</v>
       </c>
       <c r="L157" s="2" t="str">
-        <f>A157&amp;B157&amp;C157&amp;D157&amp;E157&amp;F157&amp;G157&amp;H157&amp;I157&amp;J157&amp;K157</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e156 set value {id:156,text:"合成一个轻质测重压力板",difficulty:1,criteria:"minecraft.crafted:heavy_weighted_pressure_plate",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9190,7 +9189,7 @@
         <v>223</v>
       </c>
       <c r="L158" s="2" t="str">
-        <f>A158&amp;B158&amp;C158&amp;D158&amp;E158&amp;F158&amp;G158&amp;H158&amp;I158&amp;J158&amp;K158</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e157 set value {id:157,text:"合成一个重质测重压力板",difficulty:1,criteria:"minecraft.crafted:heavy_weighted_pressure_plate",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9229,7 +9228,7 @@
         <v>223</v>
       </c>
       <c r="L159" s="2" t="str">
-        <f>A159&amp;B159&amp;C159&amp;D159&amp;E159&amp;F159&amp;G159&amp;H159&amp;I159&amp;J159&amp;K159</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e158 set value {id:158,text:"制作一个粗铁",difficulty:1,criteria:"minecraft.crafted:raw_iron",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9268,7 +9267,7 @@
         <v>223</v>
       </c>
       <c r="L160" s="2" t="str">
-        <f>A160&amp;B160&amp;C160&amp;D160&amp;E160&amp;F160&amp;G160&amp;H160&amp;I160&amp;J160&amp;K160</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e159 set value {id:159,text:"挖掘一个粗铁块",difficulty:1,criteria:"minecraft.mined:raw_iron_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9307,7 +9306,7 @@
         <v>223</v>
       </c>
       <c r="L161" s="2" t="str">
-        <f>A161&amp;B161&amp;C161&amp;D161&amp;E161&amp;F161&amp;G161&amp;H161&amp;I161&amp;J161&amp;K161</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e160 set value {id:160,text:"挖掘一个铁块",difficulty:1,criteria:"minecraft.mined:iron_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9346,7 +9345,7 @@
         <v>223</v>
       </c>
       <c r="L162" s="2" t="str">
-        <f>A162&amp;B162&amp;C162&amp;D162&amp;E162&amp;F162&amp;G162&amp;H162&amp;I162&amp;J162&amp;K162</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e161 set value {id:161,text:"制作一个粗金",difficulty:1,criteria:"minecraft.crafted:raw_gold",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9385,7 +9384,7 @@
         <v>223</v>
       </c>
       <c r="L163" s="2" t="str">
-        <f>A163&amp;B163&amp;C163&amp;D163&amp;E163&amp;F163&amp;G163&amp;H163&amp;I163&amp;J163&amp;K163</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e162 set value {id:162,text:"挖掘一个粗金块",difficulty:1,criteria:"minecraft.mined:raw_gold_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9424,7 +9423,7 @@
         <v>223</v>
       </c>
       <c r="L164" s="2" t="str">
-        <f>A164&amp;B164&amp;C164&amp;D164&amp;E164&amp;F164&amp;G164&amp;H164&amp;I164&amp;J164&amp;K164</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e163 set value {id:163,text:"挖掘一个金块",difficulty:1,criteria:"minecraft.mined:gold_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9463,7 +9462,7 @@
         <v>223</v>
       </c>
       <c r="L165" s="2" t="str">
-        <f>A165&amp;B165&amp;C165&amp;D165&amp;E165&amp;F165&amp;G165&amp;H165&amp;I165&amp;J165&amp;K165</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e164 set value {id:164,text:"制作一个粗铜",difficulty:1,criteria:"minecraft.crafted:raw_copper",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9502,7 +9501,7 @@
         <v>223</v>
       </c>
       <c r="L166" s="2" t="str">
-        <f>A166&amp;B166&amp;C166&amp;D166&amp;E166&amp;F166&amp;G166&amp;H166&amp;I166&amp;J166&amp;K166</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e165 set value {id:165,text:"挖掘一个粗铜块",difficulty:1,criteria:"minecraft.mined:raw_copper_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9541,7 +9540,7 @@
         <v>223</v>
       </c>
       <c r="L167" s="2" t="str">
-        <f>A167&amp;B167&amp;C167&amp;D167&amp;E167&amp;F167&amp;G167&amp;H167&amp;I167&amp;J167&amp;K167</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e166 set value {id:166,text:"挖掘一个铜块",difficulty:1,criteria:"minecraft.mined:copper_block",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9580,7 +9579,7 @@
         <v>223</v>
       </c>
       <c r="L168" s="2" t="str">
-        <f>A168&amp;B168&amp;C168&amp;D168&amp;E168&amp;F168&amp;G168&amp;H168&amp;I168&amp;J168&amp;K168</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e167 set value {id:167,text:"制作一个避雷针",difficulty:1,criteria:"minecraft.crafted:lightning_rod",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9619,7 +9618,7 @@
         <v>223</v>
       </c>
       <c r="L169" s="2" t="str">
-        <f>A169&amp;B169&amp;C169&amp;D169&amp;E169&amp;F169&amp;G169&amp;H169&amp;I169&amp;J169&amp;K169</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e168 set value {id:168,text:"聊天栏输入“/trigger 168”",difficulty:1,criteria:"trigger",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9658,7 +9657,7 @@
         <v>223</v>
       </c>
       <c r="L170" s="2" t="str">
-        <f>A170&amp;B170&amp;C170&amp;D170&amp;E170&amp;F170&amp;G170&amp;H170&amp;I170&amp;J170&amp;K170</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e169 set value {id:169,text:"拾取任意一种可被染色的物品(需由实体扔出)",difficulty:1,criteria:"进度",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9691,7 +9690,7 @@
         <v>223</v>
       </c>
       <c r="L171" s="2" t="str">
-        <f>A171&amp;B171&amp;C171&amp;D171&amp;E171&amp;F171&amp;G171&amp;H171&amp;I171&amp;J171&amp;K171</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e170 set value {id:170,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9724,7 +9723,7 @@
         <v>223</v>
       </c>
       <c r="L172" s="2" t="str">
-        <f>A172&amp;B172&amp;C172&amp;D172&amp;E172&amp;F172&amp;G172&amp;H172&amp;I172&amp;J172&amp;K172</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e171 set value {id:171,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9757,7 +9756,7 @@
         <v>223</v>
       </c>
       <c r="L173" s="2" t="str">
-        <f>A173&amp;B173&amp;C173&amp;D173&amp;E173&amp;F173&amp;G173&amp;H173&amp;I173&amp;J173&amp;K173</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e172 set value {id:172,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9790,7 +9789,7 @@
         <v>223</v>
       </c>
       <c r="L174" s="2" t="str">
-        <f>A174&amp;B174&amp;C174&amp;D174&amp;E174&amp;F174&amp;G174&amp;H174&amp;I174&amp;J174&amp;K174</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e173 set value {id:173,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9823,7 +9822,7 @@
         <v>223</v>
       </c>
       <c r="L175" s="2" t="str">
-        <f>A175&amp;B175&amp;C175&amp;D175&amp;E175&amp;F175&amp;G175&amp;H175&amp;I175&amp;J175&amp;K175</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e174 set value {id:174,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9856,7 +9855,7 @@
         <v>223</v>
       </c>
       <c r="L176" s="2" t="str">
-        <f>A176&amp;B176&amp;C176&amp;D176&amp;E176&amp;F176&amp;G176&amp;H176&amp;I176&amp;J176&amp;K176</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e175 set value {id:175,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9889,7 +9888,7 @@
         <v>223</v>
       </c>
       <c r="L177" s="2" t="str">
-        <f>A177&amp;B177&amp;C177&amp;D177&amp;E177&amp;F177&amp;G177&amp;H177&amp;I177&amp;J177&amp;K177</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e176 set value {id:176,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9922,7 +9921,7 @@
         <v>223</v>
       </c>
       <c r="L178" s="2" t="str">
-        <f>A178&amp;B178&amp;C178&amp;D178&amp;E178&amp;F178&amp;G178&amp;H178&amp;I178&amp;J178&amp;K178</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e177 set value {id:177,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9955,7 +9954,7 @@
         <v>223</v>
       </c>
       <c r="L179" s="2" t="str">
-        <f>A179&amp;B179&amp;C179&amp;D179&amp;E179&amp;F179&amp;G179&amp;H179&amp;I179&amp;J179&amp;K179</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e178 set value {id:178,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -9988,7 +9987,7 @@
         <v>223</v>
       </c>
       <c r="L180" s="2" t="str">
-        <f>A180&amp;B180&amp;C180&amp;D180&amp;E180&amp;F180&amp;G180&amp;H180&amp;I180&amp;J180&amp;K180</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e179 set value {id:179,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10021,7 +10020,7 @@
         <v>223</v>
       </c>
       <c r="L181" s="2" t="str">
-        <f>A181&amp;B181&amp;C181&amp;D181&amp;E181&amp;F181&amp;G181&amp;H181&amp;I181&amp;J181&amp;K181</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e180 set value {id:180,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10054,7 +10053,7 @@
         <v>223</v>
       </c>
       <c r="L182" s="2" t="str">
-        <f>A182&amp;B182&amp;C182&amp;D182&amp;E182&amp;F182&amp;G182&amp;H182&amp;I182&amp;J182&amp;K182</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e181 set value {id:181,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10087,7 +10086,7 @@
         <v>223</v>
       </c>
       <c r="L183" s="2" t="str">
-        <f>A183&amp;B183&amp;C183&amp;D183&amp;E183&amp;F183&amp;G183&amp;H183&amp;I183&amp;J183&amp;K183</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e182 set value {id:182,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10120,7 +10119,7 @@
         <v>223</v>
       </c>
       <c r="L184" s="2" t="str">
-        <f>A184&amp;B184&amp;C184&amp;D184&amp;E184&amp;F184&amp;G184&amp;H184&amp;I184&amp;J184&amp;K184</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e183 set value {id:183,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10153,7 +10152,7 @@
         <v>223</v>
       </c>
       <c r="L185" s="2" t="str">
-        <f>A185&amp;B185&amp;C185&amp;D185&amp;E185&amp;F185&amp;G185&amp;H185&amp;I185&amp;J185&amp;K185</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e184 set value {id:184,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10186,7 +10185,7 @@
         <v>223</v>
       </c>
       <c r="L186" s="2" t="str">
-        <f>A186&amp;B186&amp;C186&amp;D186&amp;E186&amp;F186&amp;G186&amp;H186&amp;I186&amp;J186&amp;K186</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e185 set value {id:185,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10219,7 +10218,7 @@
         <v>223</v>
       </c>
       <c r="L187" s="2" t="str">
-        <f>A187&amp;B187&amp;C187&amp;D187&amp;E187&amp;F187&amp;G187&amp;H187&amp;I187&amp;J187&amp;K187</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e186 set value {id:186,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10252,7 +10251,7 @@
         <v>223</v>
       </c>
       <c r="L188" s="2" t="str">
-        <f>A188&amp;B188&amp;C188&amp;D188&amp;E188&amp;F188&amp;G188&amp;H188&amp;I188&amp;J188&amp;K188</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e187 set value {id:187,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10285,7 +10284,7 @@
         <v>223</v>
       </c>
       <c r="L189" s="2" t="str">
-        <f>A189&amp;B189&amp;C189&amp;D189&amp;E189&amp;F189&amp;G189&amp;H189&amp;I189&amp;J189&amp;K189</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e188 set value {id:188,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10318,7 +10317,7 @@
         <v>223</v>
       </c>
       <c r="L190" s="2" t="str">
-        <f>A190&amp;B190&amp;C190&amp;D190&amp;E190&amp;F190&amp;G190&amp;H190&amp;I190&amp;J190&amp;K190</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e189 set value {id:189,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10351,7 +10350,7 @@
         <v>223</v>
       </c>
       <c r="L191" s="2" t="str">
-        <f>A191&amp;B191&amp;C191&amp;D191&amp;E191&amp;F191&amp;G191&amp;H191&amp;I191&amp;J191&amp;K191</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e190 set value {id:190,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10384,7 +10383,7 @@
         <v>223</v>
       </c>
       <c r="L192" s="2" t="str">
-        <f>A192&amp;B192&amp;C192&amp;D192&amp;E192&amp;F192&amp;G192&amp;H192&amp;I192&amp;J192&amp;K192</f>
+        <f t="shared" si="2"/>
         <v>data modify storage ywsj:eventlist args.e191 set value {id:191,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10417,7 +10416,7 @@
         <v>223</v>
       </c>
       <c r="L193" s="2" t="str">
-        <f>A193&amp;B193&amp;C193&amp;D193&amp;E193&amp;F193&amp;G193&amp;H193&amp;I193&amp;J193&amp;K193</f>
+        <f t="shared" ref="L193:L256" si="3">A193&amp;B193&amp;C193&amp;D193&amp;E193&amp;F193&amp;G193&amp;H193&amp;I193&amp;J193&amp;K193</f>
         <v>data modify storage ywsj:eventlist args.e192 set value {id:192,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10450,7 +10449,7 @@
         <v>223</v>
       </c>
       <c r="L194" s="2" t="str">
-        <f>A194&amp;B194&amp;C194&amp;D194&amp;E194&amp;F194&amp;G194&amp;H194&amp;I194&amp;J194&amp;K194</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e193 set value {id:193,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10483,7 +10482,7 @@
         <v>223</v>
       </c>
       <c r="L195" s="2" t="str">
-        <f>A195&amp;B195&amp;C195&amp;D195&amp;E195&amp;F195&amp;G195&amp;H195&amp;I195&amp;J195&amp;K195</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e194 set value {id:194,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10516,7 +10515,7 @@
         <v>223</v>
       </c>
       <c r="L196" s="2" t="str">
-        <f>A196&amp;B196&amp;C196&amp;D196&amp;E196&amp;F196&amp;G196&amp;H196&amp;I196&amp;J196&amp;K196</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e195 set value {id:195,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10549,7 +10548,7 @@
         <v>223</v>
       </c>
       <c r="L197" s="2" t="str">
-        <f>A197&amp;B197&amp;C197&amp;D197&amp;E197&amp;F197&amp;G197&amp;H197&amp;I197&amp;J197&amp;K197</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e196 set value {id:196,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10582,7 +10581,7 @@
         <v>223</v>
       </c>
       <c r="L198" s="2" t="str">
-        <f>A198&amp;B198&amp;C198&amp;D198&amp;E198&amp;F198&amp;G198&amp;H198&amp;I198&amp;J198&amp;K198</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e197 set value {id:197,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10615,7 +10614,7 @@
         <v>223</v>
       </c>
       <c r="L199" s="2" t="str">
-        <f>A199&amp;B199&amp;C199&amp;D199&amp;E199&amp;F199&amp;G199&amp;H199&amp;I199&amp;J199&amp;K199</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e198 set value {id:198,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10648,7 +10647,7 @@
         <v>223</v>
       </c>
       <c r="L200" s="2" t="str">
-        <f>A200&amp;B200&amp;C200&amp;D200&amp;E200&amp;F200&amp;G200&amp;H200&amp;I200&amp;J200&amp;K200</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e199 set value {id:199,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10681,7 +10680,7 @@
         <v>223</v>
       </c>
       <c r="L201" s="2" t="str">
-        <f>A201&amp;B201&amp;C201&amp;D201&amp;E201&amp;F201&amp;G201&amp;H201&amp;I201&amp;J201&amp;K201</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e200 set value {id:200,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10714,7 +10713,7 @@
         <v>223</v>
       </c>
       <c r="L202" s="2" t="str">
-        <f>A202&amp;B202&amp;C202&amp;D202&amp;E202&amp;F202&amp;G202&amp;H202&amp;I202&amp;J202&amp;K202</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e201 set value {id:201,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10747,7 +10746,7 @@
         <v>223</v>
       </c>
       <c r="L203" s="2" t="str">
-        <f>A203&amp;B203&amp;C203&amp;D203&amp;E203&amp;F203&amp;G203&amp;H203&amp;I203&amp;J203&amp;K203</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e202 set value {id:202,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10780,7 +10779,7 @@
         <v>223</v>
       </c>
       <c r="L204" s="2" t="str">
-        <f>A204&amp;B204&amp;C204&amp;D204&amp;E204&amp;F204&amp;G204&amp;H204&amp;I204&amp;J204&amp;K204</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e203 set value {id:203,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10813,7 +10812,7 @@
         <v>223</v>
       </c>
       <c r="L205" s="2" t="str">
-        <f>A205&amp;B205&amp;C205&amp;D205&amp;E205&amp;F205&amp;G205&amp;H205&amp;I205&amp;J205&amp;K205</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e204 set value {id:204,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10846,7 +10845,7 @@
         <v>223</v>
       </c>
       <c r="L206" s="2" t="str">
-        <f>A206&amp;B206&amp;C206&amp;D206&amp;E206&amp;F206&amp;G206&amp;H206&amp;I206&amp;J206&amp;K206</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e205 set value {id:205,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10879,7 +10878,7 @@
         <v>223</v>
       </c>
       <c r="L207" s="2" t="str">
-        <f>A207&amp;B207&amp;C207&amp;D207&amp;E207&amp;F207&amp;G207&amp;H207&amp;I207&amp;J207&amp;K207</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e206 set value {id:206,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10912,7 +10911,7 @@
         <v>223</v>
       </c>
       <c r="L208" s="2" t="str">
-        <f>A208&amp;B208&amp;C208&amp;D208&amp;E208&amp;F208&amp;G208&amp;H208&amp;I208&amp;J208&amp;K208</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e207 set value {id:207,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10945,7 +10944,7 @@
         <v>223</v>
       </c>
       <c r="L209" s="2" t="str">
-        <f>A209&amp;B209&amp;C209&amp;D209&amp;E209&amp;F209&amp;G209&amp;H209&amp;I209&amp;J209&amp;K209</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e208 set value {id:208,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -10978,7 +10977,7 @@
         <v>223</v>
       </c>
       <c r="L210" s="2" t="str">
-        <f>A210&amp;B210&amp;C210&amp;D210&amp;E210&amp;F210&amp;G210&amp;H210&amp;I210&amp;J210&amp;K210</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e209 set value {id:209,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11011,7 +11010,7 @@
         <v>223</v>
       </c>
       <c r="L211" s="2" t="str">
-        <f>A211&amp;B211&amp;C211&amp;D211&amp;E211&amp;F211&amp;G211&amp;H211&amp;I211&amp;J211&amp;K211</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e210 set value {id:210,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11044,7 +11043,7 @@
         <v>223</v>
       </c>
       <c r="L212" s="2" t="str">
-        <f>A212&amp;B212&amp;C212&amp;D212&amp;E212&amp;F212&amp;G212&amp;H212&amp;I212&amp;J212&amp;K212</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e211 set value {id:211,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11077,7 +11076,7 @@
         <v>223</v>
       </c>
       <c r="L213" s="2" t="str">
-        <f>A213&amp;B213&amp;C213&amp;D213&amp;E213&amp;F213&amp;G213&amp;H213&amp;I213&amp;J213&amp;K213</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e212 set value {id:212,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11110,7 +11109,7 @@
         <v>223</v>
       </c>
       <c r="L214" s="2" t="str">
-        <f>A214&amp;B214&amp;C214&amp;D214&amp;E214&amp;F214&amp;G214&amp;H214&amp;I214&amp;J214&amp;K214</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e213 set value {id:213,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11143,7 +11142,7 @@
         <v>223</v>
       </c>
       <c r="L215" s="2" t="str">
-        <f>A215&amp;B215&amp;C215&amp;D215&amp;E215&amp;F215&amp;G215&amp;H215&amp;I215&amp;J215&amp;K215</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e214 set value {id:214,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11176,7 +11175,7 @@
         <v>223</v>
       </c>
       <c r="L216" s="2" t="str">
-        <f>A216&amp;B216&amp;C216&amp;D216&amp;E216&amp;F216&amp;G216&amp;H216&amp;I216&amp;J216&amp;K216</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e215 set value {id:215,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11209,7 +11208,7 @@
         <v>223</v>
       </c>
       <c r="L217" s="2" t="str">
-        <f>A217&amp;B217&amp;C217&amp;D217&amp;E217&amp;F217&amp;G217&amp;H217&amp;I217&amp;J217&amp;K217</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e216 set value {id:216,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11242,7 +11241,7 @@
         <v>223</v>
       </c>
       <c r="L218" s="2" t="str">
-        <f>A218&amp;B218&amp;C218&amp;D218&amp;E218&amp;F218&amp;G218&amp;H218&amp;I218&amp;J218&amp;K218</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e217 set value {id:217,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11275,7 +11274,7 @@
         <v>223</v>
       </c>
       <c r="L219" s="2" t="str">
-        <f>A219&amp;B219&amp;C219&amp;D219&amp;E219&amp;F219&amp;G219&amp;H219&amp;I219&amp;J219&amp;K219</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e218 set value {id:218,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11308,7 +11307,7 @@
         <v>223</v>
       </c>
       <c r="L220" s="2" t="str">
-        <f>A220&amp;B220&amp;C220&amp;D220&amp;E220&amp;F220&amp;G220&amp;H220&amp;I220&amp;J220&amp;K220</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e219 set value {id:219,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11341,7 +11340,7 @@
         <v>223</v>
       </c>
       <c r="L221" s="2" t="str">
-        <f>A221&amp;B221&amp;C221&amp;D221&amp;E221&amp;F221&amp;G221&amp;H221&amp;I221&amp;J221&amp;K221</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e220 set value {id:220,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11374,7 +11373,7 @@
         <v>223</v>
       </c>
       <c r="L222" s="2" t="str">
-        <f>A222&amp;B222&amp;C222&amp;D222&amp;E222&amp;F222&amp;G222&amp;H222&amp;I222&amp;J222&amp;K222</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e221 set value {id:221,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11407,7 +11406,7 @@
         <v>223</v>
       </c>
       <c r="L223" s="2" t="str">
-        <f>A223&amp;B223&amp;C223&amp;D223&amp;E223&amp;F223&amp;G223&amp;H223&amp;I223&amp;J223&amp;K223</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e222 set value {id:222,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11440,7 +11439,7 @@
         <v>223</v>
       </c>
       <c r="L224" s="2" t="str">
-        <f>A224&amp;B224&amp;C224&amp;D224&amp;E224&amp;F224&amp;G224&amp;H224&amp;I224&amp;J224&amp;K224</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e223 set value {id:223,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11473,7 +11472,7 @@
         <v>223</v>
       </c>
       <c r="L225" s="2" t="str">
-        <f>A225&amp;B225&amp;C225&amp;D225&amp;E225&amp;F225&amp;G225&amp;H225&amp;I225&amp;J225&amp;K225</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e224 set value {id:224,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11506,7 +11505,7 @@
         <v>223</v>
       </c>
       <c r="L226" s="2" t="str">
-        <f>A226&amp;B226&amp;C226&amp;D226&amp;E226&amp;F226&amp;G226&amp;H226&amp;I226&amp;J226&amp;K226</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e225 set value {id:225,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11539,7 +11538,7 @@
         <v>223</v>
       </c>
       <c r="L227" s="2" t="str">
-        <f>A227&amp;B227&amp;C227&amp;D227&amp;E227&amp;F227&amp;G227&amp;H227&amp;I227&amp;J227&amp;K227</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e226 set value {id:226,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11572,7 +11571,7 @@
         <v>223</v>
       </c>
       <c r="L228" s="2" t="str">
-        <f>A228&amp;B228&amp;C228&amp;D228&amp;E228&amp;F228&amp;G228&amp;H228&amp;I228&amp;J228&amp;K228</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e227 set value {id:227,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11605,7 +11604,7 @@
         <v>223</v>
       </c>
       <c r="L229" s="2" t="str">
-        <f>A229&amp;B229&amp;C229&amp;D229&amp;E229&amp;F229&amp;G229&amp;H229&amp;I229&amp;J229&amp;K229</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e228 set value {id:228,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11638,7 +11637,7 @@
         <v>223</v>
       </c>
       <c r="L230" s="2" t="str">
-        <f>A230&amp;B230&amp;C230&amp;D230&amp;E230&amp;F230&amp;G230&amp;H230&amp;I230&amp;J230&amp;K230</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e229 set value {id:229,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11671,7 +11670,7 @@
         <v>223</v>
       </c>
       <c r="L231" s="2" t="str">
-        <f>A231&amp;B231&amp;C231&amp;D231&amp;E231&amp;F231&amp;G231&amp;H231&amp;I231&amp;J231&amp;K231</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e230 set value {id:230,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11704,7 +11703,7 @@
         <v>223</v>
       </c>
       <c r="L232" s="2" t="str">
-        <f>A232&amp;B232&amp;C232&amp;D232&amp;E232&amp;F232&amp;G232&amp;H232&amp;I232&amp;J232&amp;K232</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e231 set value {id:231,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11737,7 +11736,7 @@
         <v>223</v>
       </c>
       <c r="L233" s="2" t="str">
-        <f>A233&amp;B233&amp;C233&amp;D233&amp;E233&amp;F233&amp;G233&amp;H233&amp;I233&amp;J233&amp;K233</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e232 set value {id:232,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11770,7 +11769,7 @@
         <v>223</v>
       </c>
       <c r="L234" s="2" t="str">
-        <f>A234&amp;B234&amp;C234&amp;D234&amp;E234&amp;F234&amp;G234&amp;H234&amp;I234&amp;J234&amp;K234</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e233 set value {id:233,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11803,7 +11802,7 @@
         <v>223</v>
       </c>
       <c r="L235" s="2" t="str">
-        <f>A235&amp;B235&amp;C235&amp;D235&amp;E235&amp;F235&amp;G235&amp;H235&amp;I235&amp;J235&amp;K235</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e234 set value {id:234,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11836,7 +11835,7 @@
         <v>223</v>
       </c>
       <c r="L236" s="2" t="str">
-        <f>A236&amp;B236&amp;C236&amp;D236&amp;E236&amp;F236&amp;G236&amp;H236&amp;I236&amp;J236&amp;K236</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e235 set value {id:235,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11869,7 +11868,7 @@
         <v>223</v>
       </c>
       <c r="L237" s="2" t="str">
-        <f>A237&amp;B237&amp;C237&amp;D237&amp;E237&amp;F237&amp;G237&amp;H237&amp;I237&amp;J237&amp;K237</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e236 set value {id:236,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11902,7 +11901,7 @@
         <v>223</v>
       </c>
       <c r="L238" s="2" t="str">
-        <f>A238&amp;B238&amp;C238&amp;D238&amp;E238&amp;F238&amp;G238&amp;H238&amp;I238&amp;J238&amp;K238</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e237 set value {id:237,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11935,7 +11934,7 @@
         <v>223</v>
       </c>
       <c r="L239" s="2" t="str">
-        <f>A239&amp;B239&amp;C239&amp;D239&amp;E239&amp;F239&amp;G239&amp;H239&amp;I239&amp;J239&amp;K239</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e238 set value {id:238,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -11968,7 +11967,7 @@
         <v>223</v>
       </c>
       <c r="L240" s="2" t="str">
-        <f>A240&amp;B240&amp;C240&amp;D240&amp;E240&amp;F240&amp;G240&amp;H240&amp;I240&amp;J240&amp;K240</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e239 set value {id:239,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -12001,7 +12000,7 @@
         <v>223</v>
       </c>
       <c r="L241" s="2" t="str">
-        <f>A241&amp;B241&amp;C241&amp;D241&amp;E241&amp;F241&amp;G241&amp;H241&amp;I241&amp;J241&amp;K241</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e240 set value {id:240,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -12034,7 +12033,7 @@
         <v>223</v>
       </c>
       <c r="L242" s="2" t="str">
-        <f>A242&amp;B242&amp;C242&amp;D242&amp;E242&amp;F242&amp;G242&amp;H242&amp;I242&amp;J242&amp;K242</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e241 set value {id:241,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
@@ -12067,7 +12066,7 @@
         <v>223</v>
       </c>
       <c r="L243" s="2" t="str">
-        <f>A243&amp;B243&amp;C243&amp;D243&amp;E243&amp;F243&amp;G243&amp;H243&amp;I243&amp;J243&amp;K243</f>
+        <f t="shared" si="3"/>
         <v>data modify storage ywsj:eventlist args.e242 set value {id:242,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>

--- a/任务列表.xlsx
+++ b/任务列表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Minecraft\PCL2\.minecraft\versions\1.21.4-Fabric 0.16.9\saves\YWSJ\datapacks\sctz_ywsj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Minecraft\PCL2\.minecraft\versions\1.21.4-Fabric 0.16.9\saves\新的世界CS\datapacks\sctz_ywsj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E204CB-6B92-4A7D-8465-240B698A0605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB15909-0B77-470D-B5D9-7052E315BC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7929,7 +7929,7 @@
         <v>174</v>
       </c>
       <c r="H126" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>175</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L126" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>data modify storage ywsj:eventlist args.e125 set value {id:125,text:"飞行10距离",difficulty:2,criteria:"minecraft.custom:minecraft.fly_one_cm",args:{onlycheck:0}}</v>
+        <v>data modify storage ywsj:eventlist args.e125 set value {id:125,text:"飞行10距离",difficulty:1,criteria:"minecraft.custom:minecraft.fly_one_cm",args:{onlycheck:0}}</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
@@ -10416,7 +10416,7 @@
         <v>223</v>
       </c>
       <c r="L193" s="2" t="str">
-        <f t="shared" ref="L193:L256" si="3">A193&amp;B193&amp;C193&amp;D193&amp;E193&amp;F193&amp;G193&amp;H193&amp;I193&amp;J193&amp;K193</f>
+        <f t="shared" ref="L193:L243" si="3">A193&amp;B193&amp;C193&amp;D193&amp;E193&amp;F193&amp;G193&amp;H193&amp;I193&amp;J193&amp;K193</f>
         <v>data modify storage ywsj:eventlist args.e192 set value {id:192,text:"",difficulty:1,criteria:"",args:{onlycheck:0}}</v>
       </c>
     </row>
